--- a/artfynd/A 24304-2020 artfynd.xlsx
+++ b/artfynd/A 24304-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24304-2020 artfynd.xlsx
+++ b/artfynd/A 24304-2020 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>121159262</v>
       </c>
       <c r="B7" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>121159255</v>
       </c>
       <c r="B8" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 24304-2020 artfynd.xlsx
+++ b/artfynd/A 24304-2020 artfynd.xlsx
@@ -1305,7 +1305,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121159262</v>
+        <v>121159255</v>
       </c>
       <c r="B7" t="n">
         <v>98081</v>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455871</v>
+        <v>455945</v>
       </c>
       <c r="R7" t="n">
-        <v>6240995</v>
+        <v>6241017</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1389,6 +1389,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>förutom en samling  på ca 10 rosetter finns spridda plantor på höjden.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1416,7 +1421,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121159255</v>
+        <v>121159262</v>
       </c>
       <c r="B8" t="n">
         <v>98081</v>
@@ -1464,10 +1469,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455945</v>
+        <v>455871</v>
       </c>
       <c r="R8" t="n">
-        <v>6241017</v>
+        <v>6240995</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1500,11 +1505,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-09-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>förutom en samling  på ca 10 rosetter finns spridda plantor på höjden.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 24304-2020 artfynd.xlsx
+++ b/artfynd/A 24304-2020 artfynd.xlsx
@@ -1305,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121159255</v>
+        <v>121159262</v>
       </c>
       <c r="B7" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455945</v>
+        <v>455871</v>
       </c>
       <c r="R7" t="n">
-        <v>6241017</v>
+        <v>6240995</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1389,11 +1389,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-09-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>förutom en samling  på ca 10 rosetter finns spridda plantor på höjden.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,10 +1416,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121159262</v>
+        <v>121159255</v>
       </c>
       <c r="B8" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1469,10 +1464,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455871</v>
+        <v>455945</v>
       </c>
       <c r="R8" t="n">
-        <v>6240995</v>
+        <v>6241017</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1505,6 +1500,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>förutom en samling  på ca 10 rosetter finns spridda plantor på höjden.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 24304-2020 artfynd.xlsx
+++ b/artfynd/A 24304-2020 artfynd.xlsx
@@ -1305,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121159262</v>
+        <v>121159255</v>
       </c>
       <c r="B7" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455871</v>
+        <v>455945</v>
       </c>
       <c r="R7" t="n">
-        <v>6240995</v>
+        <v>6241017</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1389,6 +1389,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>förutom en samling  på ca 10 rosetter finns spridda plantor på höjden.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1416,10 +1421,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121159255</v>
+        <v>121159262</v>
       </c>
       <c r="B8" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1464,10 +1469,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455945</v>
+        <v>455871</v>
       </c>
       <c r="R8" t="n">
-        <v>6241017</v>
+        <v>6240995</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1500,11 +1505,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-09-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>förutom en samling  på ca 10 rosetter finns spridda plantor på höjden.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 24304-2020 artfynd.xlsx
+++ b/artfynd/A 24304-2020 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>121159255</v>
       </c>
       <c r="B7" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>121159262</v>
       </c>
       <c r="B8" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 24304-2020 artfynd.xlsx
+++ b/artfynd/A 24304-2020 artfynd.xlsx
@@ -1305,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121159255</v>
+        <v>121159262</v>
       </c>
       <c r="B7" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455945</v>
+        <v>455871</v>
       </c>
       <c r="R7" t="n">
-        <v>6241017</v>
+        <v>6240995</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1389,11 +1389,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-09-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>förutom en samling  på ca 10 rosetter finns spridda plantor på höjden.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,10 +1416,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121159262</v>
+        <v>121159255</v>
       </c>
       <c r="B8" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1469,10 +1464,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455871</v>
+        <v>455945</v>
       </c>
       <c r="R8" t="n">
-        <v>6240995</v>
+        <v>6241017</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1505,6 +1500,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>förutom en samling  på ca 10 rosetter finns spridda plantor på höjden.</t>
         </is>
       </c>
       <c r="AD8" t="b">
